--- a/excel/nhanes_diabetes_quality_review.xlsx
+++ b/excel/nhanes_diabetes_quality_review.xlsx
@@ -3105,7 +3105,7 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
